--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.01510852670861</v>
+        <v>27.51551466689234</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.58452546077546</v>
+        <v>27.81145630025179</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.9509341232938</v>
+        <v>21.58083915597023</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.53602357657852</v>
+        <v>28.94008052266105</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.87607077538717</v>
+        <v>28.00720489645503</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.87367197279427</v>
+        <v>25.01447174704114</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.36280668950117</v>
+        <v>27.70400346885862</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.73591565872987</v>
+        <v>28.57423408461178</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.82337926493047</v>
+        <v>21.33059991720743</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.73797439343378</v>
+        <v>28.96212221277759</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32.16997363113347</v>
+        <v>28.29149387066097</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.0509106980291</v>
+        <v>25.10493825262535</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.76410385852103</v>
+        <v>27.28989434103833</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.40776882192346</v>
+        <v>28.25802211203591</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28.71547005407251</v>
+        <v>21.27313994834424</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24.90673424633124</v>
+        <v>28.70443304779572</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.21202618795805</v>
+        <v>28.4272006435972</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27.92132443040508</v>
+        <v>25.19958812039205</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.06382761752365</v>
+        <v>27.40154399453787</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.80562515947178</v>
+        <v>28.5946892676984</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28.48960483098151</v>
+        <v>21.58891702561983</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.51072133370028</v>
+        <v>28.86453455410322</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.13957322683752</v>
+        <v>28.29999056640506</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.02068237356778</v>
+        <v>25.2447870926051</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24.1050038204041</v>
+        <v>27.24528641936691</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.53990870206117</v>
+        <v>33.7056274889384</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30.65531109889977</v>
+        <v>25.26760610870734</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.42161208104707</v>
+        <v>25.24420071282895</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.29448666643142</v>
+        <v>32.49589686047381</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.69441587930124</v>
+        <v>21.17520446177121</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>24.16205588767943</v>
+        <v>27.28006027081649</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>26.32445856032728</v>
+        <v>32.52677676539652</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.56690514633282</v>
+        <v>25.89036176615701</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25.23465574239203</v>
+        <v>25.12782470659361</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.17257230019577</v>
+        <v>32.94747197654592</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>27.70277609144645</v>
+        <v>21.12863585765485</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>24.20880935553868</v>
+        <v>27.0346954821531</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.25296369754073</v>
+        <v>33.01986392290021</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30.81051589562558</v>
+        <v>26.18488351398837</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.26530573088541</v>
+        <v>25.12072344766357</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.60880775583112</v>
+        <v>32.29563412837216</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>27.61845475297331</v>
+        <v>21.3477211455508</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>24.16284548746019</v>
+        <v>27.28150935994877</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>26.21270477906137</v>
+        <v>33.50783711354018</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30.8078650213446</v>
+        <v>25.765196574081</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25.11989832002448</v>
+        <v>24.95636800921303</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27.99078498601652</v>
+        <v>32.34032649337934</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28.1070682918574</v>
+        <v>20.92787807291019</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31.12209122983984</v>
+        <v>29.69337291948554</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27.06019051147196</v>
+        <v>22.57169482725498</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>23.83385468973302</v>
+        <v>20.82113903477397</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>31.85725963857454</v>
+        <v>28.48423399192464</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>35.58997359726269</v>
+        <v>31.75943239763188</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>30.00152243334276</v>
+        <v>26.55615718734973</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31.48559713053439</v>
+        <v>29.50424137872755</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>26.92284406732275</v>
+        <v>22.3323075840303</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>23.95657387032318</v>
+        <v>20.7864946041157</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32.06619041819673</v>
+        <v>28.66657287497036</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>35.08665177282037</v>
+        <v>32.82304206790047</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>29.86030132082823</v>
+        <v>26.7148932948662</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30.71637117049154</v>
+        <v>29.68195403293793</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>27.4072357282466</v>
+        <v>22.49616370095731</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>23.42606098741555</v>
+        <v>20.42058481452671</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>31.55001600419246</v>
+        <v>28.54364142778768</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>34.68057433921457</v>
+        <v>32.23480314288297</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30.14932277052732</v>
+        <v>27.32524198699894</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>31.07505028260534</v>
+        <v>29.54875460685063</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.7143326973819</v>
+        <v>22.58081077609426</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>23.54288758693267</v>
+        <v>20.81284739301471</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>31.43657753857348</v>
+        <v>28.21753972262115</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>34.82349594021068</v>
+        <v>32.58356467800201</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30.18603510123706</v>
+        <v>26.86886432652332</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>29.20182641449079</v>
+        <v>28.89136628262288</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>25.59574406755424</v>
+        <v>26.90994812286158</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.79768898976746</v>
+        <v>20.51760233117985</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>29.61087994047897</v>
+        <v>25.6201731212333</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>31.60443983773469</v>
+        <v>28.7860309413482</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>31.92202267708081</v>
+        <v>30.78260273874037</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>29.142199557174</v>
+        <v>28.38068650770089</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>25.39557299622023</v>
+        <v>27.00312068955846</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22.66715690592142</v>
+        <v>20.25392745983839</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>29.53972604319576</v>
+        <v>25.85361090628541</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30.9539699342001</v>
+        <v>28.17431352871256</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>31.16505516097175</v>
+        <v>30.1434297540413</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>29.34797170804926</v>
+        <v>28.36011465848967</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>25.72433439375112</v>
+        <v>27.28552272085795</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22.76873182606214</v>
+        <v>20.04773010566911</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>29.23956371471565</v>
+        <v>26.3871779333641</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>31.18318247093686</v>
+        <v>28.39393160443773</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>31.17541314387344</v>
+        <v>30.02576281094766</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>29.50778270483836</v>
+        <v>28.89781159991372</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>26.00329660971101</v>
+        <v>26.82264494199301</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>22.34105106920977</v>
+        <v>20.27978794446976</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>29.1891773428977</v>
+        <v>26.32408989173987</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.7874515308039</v>
+        <v>28.15805278979747</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>31.26169645690328</v>
+        <v>30.17839352713929</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="10">
   <si>
     <t>stage</t>
   </si>
@@ -26,6 +26,24 @@
   </si>
   <si>
     <t>price</t>
+  </si>
+  <si>
+    <t>ZEEBRUGGE</t>
+  </si>
+  <si>
+    <t>EMDEN</t>
+  </si>
+  <si>
+    <t>ST.FERGUS</t>
+  </si>
+  <si>
+    <t>DORNUM</t>
+  </si>
+  <si>
+    <t>DUNKERQUE</t>
+  </si>
+  <si>
+    <t>EASINGTON</t>
   </si>
 </sst>
 </file>
@@ -383,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -400,6 +418,1350 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>27.51551466689234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>27.81145630025179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>21.58083915597023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>28.94008052266105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>28.00720489645503</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>25.01447174704114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>27.70400346885862</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>28.57423408461178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>21.33059991720743</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>28.96212221277759</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>28.29149387066097</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>25.10493825262535</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>27.28989434103833</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>28.25802211203591</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>21.27313994834424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>28.70443304779572</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>28.4272006435972</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>25.19958812039205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>27.40154399453787</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>28.5946892676984</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>21.58891702561983</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>28.86453455410322</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>28.29999056640506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>25.2447870926051</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>27.24528641936691</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>33.7056274889384</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>25.26760610870734</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>25.24420071282895</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>32.49589686047381</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31">
+        <v>21.17520446177121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>27.28006027081649</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>32.52677676539652</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34">
+        <v>25.89036176615701</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35">
+        <v>25.12782470659361</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>32.94747197654592</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37">
+        <v>21.12863585765485</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38">
+        <v>27.0346954821531</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39">
+        <v>33.01986392290021</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>26.18488351398837</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>25.12072344766357</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>32.29563412837216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43">
+        <v>21.3477211455508</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44">
+        <v>27.28150935994877</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45">
+        <v>33.50783711354018</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46">
+        <v>25.765196574081</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47">
+        <v>24.95636800921303</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <v>32.34032649337934</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>20.92787807291019</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>29.69337291948554</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51">
+        <v>22.57169482725498</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52">
+        <v>20.82113903477397</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53">
+        <v>28.48423399192464</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54">
+        <v>31.75943239763188</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>26.55615718734973</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56">
+        <v>29.50424137872755</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57">
+        <v>22.3323075840303</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58">
+        <v>20.7864946041157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59">
+        <v>28.66657287497036</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60">
+        <v>32.82304206790047</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>26.7148932948662</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>29.68195403293793</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>22.49616370095731</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64">
+        <v>20.42058481452671</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>28.54364142778768</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>32.23480314288297</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67">
+        <v>27.32524198699894</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>29.54875460685063</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>22.58081077609426</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70">
+        <v>12</v>
+      </c>
+      <c r="C70" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70">
+        <v>20.81284739301471</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71">
+        <v>28.21753972262115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72">
+        <v>3</v>
+      </c>
+      <c r="B72">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72">
+        <v>32.58356467800201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73">
+        <v>3</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73">
+        <v>26.86886432652332</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74">
+        <v>28.89136628262288</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="B75">
+        <v>13</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75">
+        <v>26.90994812286158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76">
+        <v>3</v>
+      </c>
+      <c r="B76">
+        <v>13</v>
+      </c>
+      <c r="C76" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76">
+        <v>20.51760233117985</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77">
+        <v>3</v>
+      </c>
+      <c r="B77">
+        <v>13</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77">
+        <v>25.6201731212333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78">
+        <v>13</v>
+      </c>
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78">
+        <v>28.7860309413482</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79">
+        <v>3</v>
+      </c>
+      <c r="B79">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>30.78260273874037</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>14</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80">
+        <v>28.38068650770089</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81">
+        <v>3</v>
+      </c>
+      <c r="B81">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81">
+        <v>27.00312068955846</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>3</v>
+      </c>
+      <c r="B82">
+        <v>14</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82">
+        <v>20.25392745983839</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>3</v>
+      </c>
+      <c r="B83">
+        <v>14</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83">
+        <v>25.85361090628541</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>14</v>
+      </c>
+      <c r="C84" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84">
+        <v>28.17431352871256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85">
+        <v>3</v>
+      </c>
+      <c r="B85">
+        <v>14</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85">
+        <v>30.1434297540413</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86">
+        <v>3</v>
+      </c>
+      <c r="B86">
+        <v>15</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86">
+        <v>28.36011465848967</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87">
+        <v>3</v>
+      </c>
+      <c r="B87">
+        <v>15</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87">
+        <v>27.28552272085795</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88">
+        <v>3</v>
+      </c>
+      <c r="B88">
+        <v>15</v>
+      </c>
+      <c r="C88" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88">
+        <v>20.04773010566911</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="B89">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>26.3871779333641</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90">
+        <v>3</v>
+      </c>
+      <c r="B90">
+        <v>15</v>
+      </c>
+      <c r="C90" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90">
+        <v>28.39393160443773</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91">
+        <v>3</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91">
+        <v>30.02576281094766</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92">
+        <v>3</v>
+      </c>
+      <c r="B92">
+        <v>16</v>
+      </c>
+      <c r="C92" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92">
+        <v>28.89781159991372</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="B93">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93">
+        <v>26.82264494199301</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94">
+        <v>3</v>
+      </c>
+      <c r="B94">
+        <v>16</v>
+      </c>
+      <c r="C94" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94">
+        <v>20.27978794446976</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95">
+        <v>3</v>
+      </c>
+      <c r="B95">
+        <v>16</v>
+      </c>
+      <c r="C95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95">
+        <v>26.32408989173987</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96">
+        <v>3</v>
+      </c>
+      <c r="B96">
+        <v>16</v>
+      </c>
+      <c r="C96" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96">
+        <v>28.15805278979747</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97">
+        <v>3</v>
+      </c>
+      <c r="B97">
+        <v>16</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97">
+        <v>30.17839352713929</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.18355546608835</v>
+        <v>29.83514143619801</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.39517470675498</v>
+        <v>31.49993439066483</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.8409441013374</v>
+        <v>28.00408248136415</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.15579529138947</v>
+        <v>28.37558352550994</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.12564475525815</v>
+        <v>31.84773281933385</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.48367580209327</v>
+        <v>27.74250134561253</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.93640333555905</v>
+        <v>29.8391662908838</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.64867405874071</v>
+        <v>31.77318182003393</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23.48583466284178</v>
+        <v>27.833659494094</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.48245336085019</v>
+        <v>28.52394221384186</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30.44891753555758</v>
+        <v>31.95789290869828</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22.62799802620027</v>
+        <v>27.70847003502016</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.33971889302471</v>
+        <v>29.88410496737066</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.33513965493799</v>
+        <v>31.76407241933509</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23.81517252346108</v>
+        <v>28.45385965931724</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.94959100318169</v>
+        <v>28.31321702093187</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.40047368735088</v>
+        <v>32.1483433834975</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22.57792680758135</v>
+        <v>28.13983607251739</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.26959890337854</v>
+        <v>30.01883331098367</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>26.58196565709155</v>
+        <v>31.63825763146389</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.77758690468968</v>
+        <v>27.92018561357627</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.42632144615377</v>
+        <v>28.63139205480966</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.17166786439989</v>
+        <v>31.84333309134808</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>22.723863505453</v>
+        <v>27.63337915363857</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.13214079690126</v>
+        <v>30.6438372609827</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27.93021324424594</v>
+        <v>22.40858265905051</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25.15273319898849</v>
+        <v>19.97121133222409</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.35396272366441</v>
+        <v>30.3466613501259</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.1318412597928</v>
+        <v>25.5996755648541</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.82081737615756</v>
+        <v>27.4286690910601</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.90180970200738</v>
+        <v>32.02442987550816</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27.74204982391661</v>
+        <v>22.20583610267503</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25.1407436757067</v>
+        <v>19.85473690863989</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25.98719433613161</v>
+        <v>30.54397225757848</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.51595022669583</v>
+        <v>25.80981860032336</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28.85165492504793</v>
+        <v>27.46324130127046</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.14209825081874</v>
+        <v>30.95937552477209</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27.74564621528348</v>
+        <v>22.49087569144612</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>24.55718346727586</v>
+        <v>19.66625770713721</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.20217484933838</v>
+        <v>31.00614019186134</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27.74081900635244</v>
+        <v>25.93813726956136</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28.84427659700714</v>
+        <v>27.72219179835322</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>29.78981058464128</v>
+        <v>31.38437463376011</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.32637755182649</v>
+        <v>22.52730196344103</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25.15005710675999</v>
+        <v>20.28246286563605</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25.40304133320891</v>
+        <v>31.18633255548512</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.50415636183085</v>
+        <v>25.5962086178778</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28.30598998412841</v>
+        <v>27.8151673889444</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30.52441074403471</v>
+        <v>27.731179768609</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>25.45758779607953</v>
+        <v>25.40637892859768</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25.99723558342902</v>
+        <v>27.08847739672359</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30.44819833522931</v>
+        <v>28.45806158671226</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25.07638044817486</v>
+        <v>35.21110143066785</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>28.00232950675672</v>
+        <v>23.65782612153435</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>30.64535875335127</v>
+        <v>27.79890668696608</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25.83648693880004</v>
+        <v>25.49079726700536</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>26.43538576007058</v>
+        <v>27.47040493094257</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.17860798266956</v>
+        <v>28.88396812713716</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>24.87698167212281</v>
+        <v>35.93734619271077</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>27.88013612181757</v>
+        <v>23.80791365797615</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30.70551918588674</v>
+        <v>28.56825472332281</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25.0465741818617</v>
+        <v>25.40331954046304</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>26.40628045758505</v>
+        <v>27.57990226335423</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>29.96009050201009</v>
+        <v>28.61133581462</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>25.11148976084025</v>
+        <v>36.14041039494401</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>28.21292754717938</v>
+        <v>23.74259785980485</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30.76861835408234</v>
+        <v>27.55766821663608</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>25.13400066064247</v>
+        <v>25.10535124591006</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>26.3161830233172</v>
+        <v>26.87900855061505</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>29.80923805234182</v>
+        <v>28.36190918656374</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>24.88074734405518</v>
+        <v>36.56428953811697</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>28.22519827114435</v>
+        <v>23.68232333780508</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>27.28337143724762</v>
+        <v>33.19321063842342</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29.32473676471755</v>
+        <v>29.0361779286318</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>23.22350117614859</v>
+        <v>22.98030717468211</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>23.25739925642721</v>
+        <v>30.12523510816581</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>25.22121667180866</v>
+        <v>31.48124602626633</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>26.67901778267959</v>
+        <v>25.96751203845078</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>26.86886143344152</v>
+        <v>33.37523746850765</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>29.22928740226975</v>
+        <v>28.73735075885862</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22.61376938092832</v>
+        <v>23.28038622460837</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>23.2896173845673</v>
+        <v>29.60680437661528</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>25.28173214698845</v>
+        <v>31.60398665500326</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>26.17297503889117</v>
+        <v>25.85543041194362</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>27.15420209864659</v>
+        <v>33.2025959647558</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>29.26455766736397</v>
+        <v>28.71108852363582</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>23.58638184305465</v>
+        <v>23.44650056206392</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>22.97598163713795</v>
+        <v>30.19414015975209</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>25.14484978461089</v>
+        <v>32.22720619763651</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>26.37759165371961</v>
+        <v>26.26976058016082</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>27.20864066004928</v>
+        <v>32.56599521274889</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29.66394074079184</v>
+        <v>28.62013356116862</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>22.84129606884754</v>
+        <v>23.43494548994419</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>23.05451480377034</v>
+        <v>29.95672368049244</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>25.59008779317856</v>
+        <v>30.7563253747994</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>26.53986358757479</v>
+        <v>26.49255740681477</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.83514143619801</v>
+        <v>24.12059235402448</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.49993439066483</v>
+        <v>27.60559786571805</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.00408248136415</v>
+        <v>22.17157684616676</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.37558352550994</v>
+        <v>25.04528517870058</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.84773281933385</v>
+        <v>30.55460416378444</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.74250134561253</v>
+        <v>31.44156640180848</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.8391662908838</v>
+        <v>23.92131245609947</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31.77318182003393</v>
+        <v>27.54086209206778</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.833659494094</v>
+        <v>21.83389483228672</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28.52394221384186</v>
+        <v>25.34576860219214</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31.95789290869828</v>
+        <v>30.1598105712166</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.70847003502016</v>
+        <v>31.21103706615447</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29.88410496737066</v>
+        <v>23.91735787361109</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31.76407241933509</v>
+        <v>27.97276368770047</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28.45385965931724</v>
+        <v>22.07917956628714</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28.31321702093187</v>
+        <v>25.22076183712727</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.1483433834975</v>
+        <v>30.33400055546253</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.13983607251739</v>
+        <v>31.51649345887813</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.01883331098367</v>
+        <v>23.88918658148304</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31.63825763146389</v>
+        <v>28.31938411214121</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.92018561357627</v>
+        <v>21.88150701336459</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.63139205480966</v>
+        <v>24.98712609552976</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31.84333309134808</v>
+        <v>30.73323590036054</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.63337915363857</v>
+        <v>31.55886104438118</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.6438372609827</v>
+        <v>31.60445030704517</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22.40858265905051</v>
+        <v>23.57195725157398</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19.97121133222409</v>
+        <v>22.15015032454063</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.3466613501259</v>
+        <v>30.58912649897518</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>25.5996755648541</v>
+        <v>27.31329158198917</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.4286690910601</v>
+        <v>25.67930098237081</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>32.02442987550816</v>
+        <v>31.48659887480184</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>22.20583610267503</v>
+        <v>23.27928921494863</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19.85473690863989</v>
+        <v>22.12090422436545</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>30.54397225757848</v>
+        <v>31.4244315950212</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>25.80981860032336</v>
+        <v>26.83512345294028</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>27.46324130127046</v>
+        <v>25.53574128554948</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.95937552477209</v>
+        <v>32.19433054849551</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>22.49087569144612</v>
+        <v>23.47193710087418</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19.66625770713721</v>
+        <v>22.26642568305248</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.00614019186134</v>
+        <v>31.13300494236139</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.93813726956136</v>
+        <v>26.94997414387066</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>27.72219179835322</v>
+        <v>25.07278332639012</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>31.38437463376011</v>
+        <v>31.47893984232407</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22.52730196344103</v>
+        <v>23.36308935488745</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20.28246286563605</v>
+        <v>21.99669729541311</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>31.18633255548512</v>
+        <v>30.25921551498749</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>25.5962086178778</v>
+        <v>27.06175826252606</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>27.8151673889444</v>
+        <v>24.93048317391629</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27.731179768609</v>
+        <v>30.6666782401041</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>25.40637892859768</v>
+        <v>24.89517074724254</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27.08847739672359</v>
+        <v>26.49835313455079</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28.45806158671226</v>
+        <v>24.46698215468443</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>35.21110143066785</v>
+        <v>27.63374541855596</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23.65782612153435</v>
+        <v>27.34906929611826</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>27.79890668696608</v>
+        <v>30.97075827026875</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25.49079726700536</v>
+        <v>24.98273381798739</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>27.47040493094257</v>
+        <v>26.85270697285837</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.88396812713716</v>
+        <v>24.36640243969373</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>35.93734619271077</v>
+        <v>27.99711265097849</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>23.80791365797615</v>
+        <v>27.23195405916766</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>28.56825472332281</v>
+        <v>30.76597204961756</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25.40331954046304</v>
+        <v>25.3078562527965</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>27.57990226335423</v>
+        <v>26.55325512773563</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>28.61133581462</v>
+        <v>24.04132966544545</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>36.14041039494401</v>
+        <v>28.24364987176533</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>23.74259785980485</v>
+        <v>26.86195264007092</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27.55766821663608</v>
+        <v>30.56112130565326</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>25.10535124591006</v>
+        <v>25.06004961743668</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>26.87900855061505</v>
+        <v>26.21670392213645</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28.36190918656374</v>
+        <v>24.56466326861284</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>36.56428953811697</v>
+        <v>28.50360174644338</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>23.68232333780508</v>
+        <v>27.41312231788384</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>33.19321063842342</v>
+        <v>24.11400884528933</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29.0361779286318</v>
+        <v>29.14083254236348</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.98030717468211</v>
+        <v>26.23788890600082</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30.12523510816581</v>
+        <v>29.58884492897959</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>31.48124602626633</v>
+        <v>31.38312118415516</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25.96751203845078</v>
+        <v>31.4433354050359</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>33.37523746850765</v>
+        <v>24.4271403584064</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>28.73735075885862</v>
+        <v>29.14296423249249</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23.28038622460837</v>
+        <v>25.95803094390131</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>29.60680437661528</v>
+        <v>29.50192165269881</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>31.60398665500326</v>
+        <v>30.8889316714355</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>25.85543041194362</v>
+        <v>31.61978825534636</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>33.2025959647558</v>
+        <v>24.18869144148197</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>28.71108852363582</v>
+        <v>28.84416555367423</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>23.44650056206392</v>
+        <v>25.44740548942339</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>30.19414015975209</v>
+        <v>29.69706792684493</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.22720619763651</v>
+        <v>30.3333206389965</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>26.26976058016082</v>
+        <v>30.64585916386323</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>32.56599521274889</v>
+        <v>24.47505487289407</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>28.62013356116862</v>
+        <v>29.96211602382724</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>23.43494548994419</v>
+        <v>25.92183879673984</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>29.95672368049244</v>
+        <v>29.79472050564764</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.7563253747994</v>
+        <v>30.69684089225706</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>26.49255740681477</v>
+        <v>31.28917529148135</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.12059235402448</v>
+        <v>24.42214021409653</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.60559786571805</v>
+        <v>29.58156984296707</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.17157684616676</v>
+        <v>27.56378116457381</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.04528517870058</v>
+        <v>31.00904808484093</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.55460416378444</v>
+        <v>30.77584248476237</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.44156640180848</v>
+        <v>24.6222160311808</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23.92131245609947</v>
+        <v>24.03154526590657</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.54086209206778</v>
+        <v>29.17900605034385</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.83389483228672</v>
+        <v>27.25281660882665</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.34576860219214</v>
+        <v>31.2046527044548</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30.1598105712166</v>
+        <v>31.68274025966101</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31.21103706615447</v>
+        <v>24.96116399500684</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23.91735787361109</v>
+        <v>24.17831649613185</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27.97276368770047</v>
+        <v>28.7544126986065</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22.07917956628714</v>
+        <v>27.940031920046</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.22076183712727</v>
+        <v>30.8085711004083</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.33400055546253</v>
+        <v>30.92289902051513</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31.51649345887813</v>
+        <v>25.22046726589283</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>23.88918658148304</v>
+        <v>24.24966924498394</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28.31938411214121</v>
+        <v>29.76796129530018</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.88150701336459</v>
+        <v>27.52789042189582</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.98712609552976</v>
+        <v>31.19401297094789</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.73323590036054</v>
+        <v>31.46819443374011</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.55886104438118</v>
+        <v>25.33707891221163</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.60445030704517</v>
+        <v>28.33159164328176</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23.57195725157398</v>
+        <v>35.88336837272493</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22.15015032454063</v>
+        <v>26.26379350210652</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.58912649897518</v>
+        <v>29.64110816731757</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27.31329158198917</v>
+        <v>23.97072796643558</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.67930098237081</v>
+        <v>22.68659169596339</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.48659887480184</v>
+        <v>28.39592322903366</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>23.27928921494863</v>
+        <v>35.89107775634042</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>22.12090422436545</v>
+        <v>25.91984589609029</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>31.4244315950212</v>
+        <v>29.35680798671917</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>26.83512345294028</v>
+        <v>24.09802251929222</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25.53574128554948</v>
+        <v>22.75670647876124</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>32.19433054849551</v>
+        <v>28.80264615102018</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>23.47193710087418</v>
+        <v>35.66831022162638</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>22.26642568305248</v>
+        <v>25.97123603570743</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.13300494236139</v>
+        <v>29.69045604817319</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>26.94997414387066</v>
+        <v>24.06446683319715</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25.07278332639012</v>
+        <v>22.82660666970417</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>31.47893984232407</v>
+        <v>28.38631687451952</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>23.36308935488745</v>
+        <v>35.44373576753897</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>21.99669729541311</v>
+        <v>26.17487046479141</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30.25921551498749</v>
+        <v>29.27860195159983</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27.06175826252606</v>
+        <v>23.58638584884688</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>24.93048317391629</v>
+        <v>22.86212877117175</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30.6666782401041</v>
+        <v>30.23859394561126</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>24.89517074724254</v>
+        <v>23.61448362830918</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>26.49835313455079</v>
+        <v>27.97518765860608</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>24.46698215468443</v>
+        <v>25.62862892871181</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27.63374541855596</v>
+        <v>26.78871557141616</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>27.34906929611826</v>
+        <v>23.6425443037436</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>30.97075827026875</v>
+        <v>30.47526180877527</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>24.98273381798739</v>
+        <v>23.63098214534314</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>26.85270697285837</v>
+        <v>28.19016132591789</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.36640243969373</v>
+        <v>25.6047240097758</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>27.99711265097849</v>
+        <v>27.28819466744117</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>27.23195405916766</v>
+        <v>23.10014917955383</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30.76597204961756</v>
+        <v>30.10466297648259</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25.3078562527965</v>
+        <v>23.35906790280313</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>26.55325512773563</v>
+        <v>28.08461288626504</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>24.04132966544545</v>
+        <v>26.16428620926767</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>28.24364987176533</v>
+        <v>26.71533135313179</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>26.86195264007092</v>
+        <v>23.7643461549039</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30.56112130565326</v>
+        <v>30.21854929820696</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>25.06004961743668</v>
+        <v>23.62302929334229</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>26.21670392213645</v>
+        <v>27.58712710398419</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>24.56466326861284</v>
+        <v>25.93752489817568</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.50360174644338</v>
+        <v>26.99722638470807</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>27.41312231788384</v>
+        <v>22.89827068656533</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>24.11400884528933</v>
+        <v>33.93099153457082</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29.14083254236348</v>
+        <v>29.05927978695961</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>26.23788890600082</v>
+        <v>22.37799007184676</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>29.58884492897959</v>
+        <v>30.29877912036161</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>31.38312118415516</v>
+        <v>32.29645191838703</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>31.4433354050359</v>
+        <v>24.81964789103086</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>24.4271403584064</v>
+        <v>33.76927561708727</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>29.14296423249249</v>
+        <v>29.04160525728512</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>25.95803094390131</v>
+        <v>22.58661869813195</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>29.50192165269881</v>
+        <v>29.725267433076</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30.8889316714355</v>
+        <v>32.96581398241127</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>31.61978825534636</v>
+        <v>24.48854292508366</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>24.18869144148197</v>
+        <v>33.77253404171745</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>28.84416555367423</v>
+        <v>29.15052630615687</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>25.44740548942339</v>
+        <v>22.67597200516736</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>29.69706792684493</v>
+        <v>29.85483153399918</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>30.3333206389965</v>
+        <v>32.19015202157992</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>30.64585916386323</v>
+        <v>25.06401571685797</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24.47505487289407</v>
+        <v>32.92194871967974</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29.96211602382724</v>
+        <v>28.6159923182355</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>25.92183879673984</v>
+        <v>22.45900610048965</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>29.79472050564764</v>
+        <v>30.18452239821874</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.69684089225706</v>
+        <v>32.31376739798289</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>31.28917529148135</v>
+        <v>24.66391719484946</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -451,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.42214021409653</v>
+        <v>27.51551466689234</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.58156984296707</v>
+        <v>27.81145630025179</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.56378116457381</v>
+        <v>21.58083915597023</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.00904808484093</v>
+        <v>28.94008052266105</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.77584248476237</v>
+        <v>28.00720489645503</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.6222160311808</v>
+        <v>25.01447174704114</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.03154526590657</v>
+        <v>27.70400346885862</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.17900605034385</v>
+        <v>28.57423408461178</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.25281660882665</v>
+        <v>21.33059991720743</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.2046527044548</v>
+        <v>28.96212221277759</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31.68274025966101</v>
+        <v>28.29149387066097</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.96116399500684</v>
+        <v>25.10493825262535</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24.17831649613185</v>
+        <v>27.28989434103833</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.7544126986065</v>
+        <v>28.25802211203591</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27.940031920046</v>
+        <v>21.27313994834424</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.8085711004083</v>
+        <v>28.70443304779572</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.92289902051513</v>
+        <v>28.4272006435972</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25.22046726589283</v>
+        <v>25.19958812039205</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24.24966924498394</v>
+        <v>27.40154399453787</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.76796129530018</v>
+        <v>28.5946892676984</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.52789042189582</v>
+        <v>21.58891702561983</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31.19401297094789</v>
+        <v>28.86453455410322</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31.46819443374011</v>
+        <v>28.29999056640506</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.33707891221163</v>
+        <v>25.2447870926051</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.33159164328176</v>
+        <v>27.24528641936691</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35.88336837272493</v>
+        <v>33.7056274889384</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.26379350210652</v>
+        <v>25.26760610870734</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.64110816731757</v>
+        <v>25.24420071282895</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>23.97072796643558</v>
+        <v>32.49589686047381</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22.68659169596339</v>
+        <v>21.17520446177121</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28.39592322903366</v>
+        <v>27.28006027081649</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>35.89107775634042</v>
+        <v>32.52677676539652</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25.91984589609029</v>
+        <v>25.89036176615701</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29.35680798671917</v>
+        <v>25.12782470659361</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>24.09802251929222</v>
+        <v>32.94747197654592</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>22.75670647876124</v>
+        <v>21.12863585765485</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.80264615102018</v>
+        <v>27.0346954821531</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>35.66831022162638</v>
+        <v>33.01986392290021</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25.97123603570743</v>
+        <v>26.18488351398837</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29.69045604817319</v>
+        <v>25.12072344766357</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>24.06446683319715</v>
+        <v>32.29563412837216</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22.82660666970417</v>
+        <v>21.3477211455508</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28.38631687451952</v>
+        <v>27.28150935994877</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>35.44373576753897</v>
+        <v>33.50783711354018</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>26.17487046479141</v>
+        <v>25.765196574081</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>29.27860195159983</v>
+        <v>24.95636800921303</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>23.58638584884688</v>
+        <v>32.34032649337934</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>22.86212877117175</v>
+        <v>20.92787807291019</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30.23859394561126</v>
+        <v>29.69337291948554</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>23.61448362830918</v>
+        <v>22.57169482725498</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27.97518765860608</v>
+        <v>20.82113903477397</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>25.62862892871181</v>
+        <v>28.48423399192464</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>26.78871557141616</v>
+        <v>31.75943239763188</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23.6425443037436</v>
+        <v>26.55615718734973</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>30.47526180877527</v>
+        <v>29.50424137872755</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>23.63098214534314</v>
+        <v>22.3323075840303</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>28.19016132591789</v>
+        <v>20.7864946041157</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>25.6047240097758</v>
+        <v>28.66657287497036</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>27.28819466744117</v>
+        <v>32.82304206790047</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>23.10014917955383</v>
+        <v>26.7148932948662</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30.10466297648259</v>
+        <v>29.68195403293793</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>23.35906790280313</v>
+        <v>22.49616370095731</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>28.08461288626504</v>
+        <v>20.42058481452671</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>26.16428620926767</v>
+        <v>28.54364142778768</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>26.71533135313179</v>
+        <v>32.23480314288297</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>23.7643461549039</v>
+        <v>27.32524198699894</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30.21854929820696</v>
+        <v>29.54875460685063</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>23.62302929334229</v>
+        <v>22.58081077609426</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>27.58712710398419</v>
+        <v>20.81284739301471</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>25.93752489817568</v>
+        <v>28.21753972262115</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>26.99722638470807</v>
+        <v>32.58356467800201</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.89827068656533</v>
+        <v>26.86886432652332</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>33.93099153457082</v>
+        <v>28.89136628262288</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29.05927978695961</v>
+        <v>26.90994812286158</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.37799007184676</v>
+        <v>20.51760233117985</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30.29877912036161</v>
+        <v>25.6201731212333</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.29645191838703</v>
+        <v>28.7860309413482</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>24.81964789103086</v>
+        <v>30.78260273874037</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>33.76927561708727</v>
+        <v>28.38068650770089</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>29.04160525728512</v>
+        <v>27.00312068955846</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22.58661869813195</v>
+        <v>20.25392745983839</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>29.725267433076</v>
+        <v>25.85361090628541</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>32.96581398241127</v>
+        <v>28.17431352871256</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24.48854292508366</v>
+        <v>30.1434297540413</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>33.77253404171745</v>
+        <v>28.36011465848967</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>29.15052630615687</v>
+        <v>27.28552272085795</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22.67597200516736</v>
+        <v>20.04773010566911</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>29.85483153399918</v>
+        <v>26.3871779333641</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.19015202157992</v>
+        <v>28.39393160443773</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>25.06401571685797</v>
+        <v>30.02576281094766</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>32.92194871967974</v>
+        <v>28.89781159991372</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>28.6159923182355</v>
+        <v>26.82264494199301</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>22.45900610048965</v>
+        <v>20.27978794446976</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>30.18452239821874</v>
+        <v>26.32408989173987</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>32.31376739798289</v>
+        <v>28.15805278979747</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>24.66391719484946</v>
+        <v>30.17839352713929</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.51551466689234</v>
+        <v>31.43459126323116</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.81145630025179</v>
+        <v>30.53864085904335</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.58083915597023</v>
+        <v>25.56613190494289</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.94008052266105</v>
+        <v>30.04858826011586</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.00720489645503</v>
+        <v>31.95960313976598</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.01447174704114</v>
+        <v>21.54599341268699</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.70400346885862</v>
+        <v>31.24316120970374</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.57423408461178</v>
+        <v>30.63208495764209</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.33059991720743</v>
+        <v>25.45129340542299</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28.96212221277759</v>
+        <v>30.04042264629414</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.29149387066097</v>
+        <v>32.57939311805275</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.10493825262535</v>
+        <v>21.6599837499657</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.28989434103833</v>
+        <v>31.64334791406234</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.25802211203591</v>
+        <v>29.97347131352071</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21.27313994834424</v>
+        <v>25.48446407807261</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28.70443304779572</v>
+        <v>30.06403860144275</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.4272006435972</v>
+        <v>32.17423613821017</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25.19958812039205</v>
+        <v>21.79154502514103</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.40154399453787</v>
+        <v>31.83178308462408</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28.5946892676984</v>
+        <v>30.53435024909721</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.58891702561983</v>
+        <v>25.53226797267805</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.86453455410322</v>
+        <v>30.57635874120717</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.29999056640506</v>
+        <v>31.74249373995244</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.2447870926051</v>
+        <v>21.83855582813229</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.24528641936691</v>
+        <v>24.69733223346534</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33.7056274889384</v>
+        <v>29.01648619857582</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25.26760610870734</v>
+        <v>27.30021093549698</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.24420071282895</v>
+        <v>28.10803562548862</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32.49589686047381</v>
+        <v>31.11209637823022</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.17520446177121</v>
+        <v>23.50352667353693</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.28006027081649</v>
+        <v>24.86464487200095</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>32.52677676539652</v>
+        <v>28.30393753363398</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25.89036176615701</v>
+        <v>27.13805050798108</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25.12782470659361</v>
+        <v>28.41051555128375</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32.94747197654592</v>
+        <v>31.12862547197211</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>21.12863585765485</v>
+        <v>23.26562886367351</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.0346954821531</v>
+        <v>24.84183937187003</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>33.01986392290021</v>
+        <v>28.09743470581513</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>26.18488351398837</v>
+        <v>27.04212756346818</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.12072344766357</v>
+        <v>28.40555107389931</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>32.29563412837216</v>
+        <v>30.28711359509088</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>21.3477211455508</v>
+        <v>22.60453722602316</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.28150935994877</v>
+        <v>24.85231018371906</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>33.50783711354018</v>
+        <v>28.33935632871305</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25.765196574081</v>
+        <v>27.07059987099989</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>24.95636800921303</v>
+        <v>28.11016181527857</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.34032649337934</v>
+        <v>31.47959024504506</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20.92787807291019</v>
+        <v>23.38570942280567</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>29.69337291948554</v>
+        <v>26.1371467581629</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>22.57169482725498</v>
+        <v>28.03970894712026</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20.82113903477397</v>
+        <v>28.212374127325</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28.48423399192464</v>
+        <v>28.84210424282772</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31.75943239763188</v>
+        <v>26.69020429004637</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>26.55615718734973</v>
+        <v>19.75219788355927</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29.50424137872755</v>
+        <v>26.42486760863856</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>22.3323075840303</v>
+        <v>28.02967681343226</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>20.7864946041157</v>
+        <v>28.39713287858624</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.66657287497036</v>
+        <v>28.2031900523051</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>32.82304206790047</v>
+        <v>27.68916018813398</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>26.7148932948662</v>
+        <v>19.43931321348244</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>29.68195403293793</v>
+        <v>26.0905846833175</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>22.49616370095731</v>
+        <v>28.62041872317977</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20.42058481452671</v>
+        <v>27.8724109715357</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>28.54364142778768</v>
+        <v>29.60361593354917</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32.23480314288297</v>
+        <v>27.3618845742841</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>27.32524198699894</v>
+        <v>19.54818143265341</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>29.54875460685063</v>
+        <v>26.02593266782886</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>22.58081077609426</v>
+        <v>28.19068770570833</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>20.81284739301471</v>
+        <v>28.44119056595101</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28.21753972262115</v>
+        <v>28.47279589487055</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>32.58356467800201</v>
+        <v>27.05228344350408</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>26.86886432652332</v>
+        <v>19.14166797427867</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.89136628262288</v>
+        <v>25.32133056938052</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26.90994812286158</v>
+        <v>29.49476501632238</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>20.51760233117985</v>
+        <v>29.36333097722495</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25.6201731212333</v>
+        <v>30.05243924239526</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>28.7860309413482</v>
+        <v>29.93940170619767</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>30.78260273874037</v>
+        <v>23.98833981925803</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28.38068650770089</v>
+        <v>25.30117297900549</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>27.00312068955846</v>
+        <v>30.19367348056218</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>20.25392745983839</v>
+        <v>29.66163319429181</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>25.85361090628541</v>
+        <v>29.68374460842151</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>28.17431352871256</v>
+        <v>29.46502631388352</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>30.1434297540413</v>
+        <v>24.25869794806401</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>28.36011465848967</v>
+        <v>25.68709171745893</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>27.28552272085795</v>
+        <v>30.35461276894996</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>20.04773010566911</v>
+        <v>29.75937443603431</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26.3871779333641</v>
+        <v>29.56286719937211</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>28.39393160443773</v>
+        <v>29.77249555715134</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>30.02576281094766</v>
+        <v>24.04908380857763</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28.89781159991372</v>
+        <v>25.26614135341444</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>26.82264494199301</v>
+        <v>29.96696325590481</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>20.27978794446976</v>
+        <v>29.09383101197953</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26.32408989173987</v>
+        <v>30.04868318147007</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>28.15805278979747</v>
+        <v>30.04444271535057</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30.17839352713929</v>
+        <v>23.85399680796633</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.43459126323116</v>
+        <v>31.65046748039528</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.53864085904335</v>
+        <v>26.24656289412541</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.56613190494289</v>
+        <v>25.59733377173156</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.04858826011586</v>
+        <v>25.29044511696442</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.95960313976598</v>
+        <v>28.86276231189549</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.54599341268699</v>
+        <v>27.9703314553703</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.24316120970374</v>
+        <v>31.54644560041393</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30.63208495764209</v>
+        <v>26.23858595052071</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.45129340542299</v>
+        <v>25.73484279650808</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30.04042264629414</v>
+        <v>25.61615785453955</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32.57939311805275</v>
+        <v>29.27971679549439</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.6599837499657</v>
+        <v>28.31683116174625</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.64334791406234</v>
+        <v>31.37399833765323</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>29.97347131352071</v>
+        <v>26.41237969365224</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.48446407807261</v>
+        <v>25.65163154539501</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.06403860144275</v>
+        <v>25.30419008282835</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32.17423613821017</v>
+        <v>29.33896515943905</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21.79154502514103</v>
+        <v>28.04717455991932</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.83178308462408</v>
+        <v>31.9702183921431</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>30.53435024909721</v>
+        <v>26.48201475215965</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.53226797267805</v>
+        <v>26.07850287784662</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30.57635874120717</v>
+        <v>25.02541697054046</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31.74249373995244</v>
+        <v>28.77470744571601</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21.83855582813229</v>
+        <v>27.92679089301319</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24.69733223346534</v>
+        <v>27.03738452070349</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.01648619857582</v>
+        <v>27.12468397564772</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27.30021093549698</v>
+        <v>23.3936326227774</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.10803562548862</v>
+        <v>25.11506478789694</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31.11209637823022</v>
+        <v>27.90056655146273</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23.50352667353693</v>
+        <v>26.16547251859039</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>24.86464487200095</v>
+        <v>27.056296015821</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.30393753363398</v>
+        <v>27.09398799783844</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>27.13805050798108</v>
+        <v>23.2681794878276</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.41051555128375</v>
+        <v>25.58196303637139</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31.12862547197211</v>
+        <v>28.0384731664301</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>23.26562886367351</v>
+        <v>26.05701896004416</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>24.84183937187003</v>
+        <v>27.04771321096216</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28.09743470581513</v>
+        <v>26.92109046683074</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>27.04212756346818</v>
+        <v>23.16362784684978</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28.40555107389931</v>
+        <v>25.73020673079117</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30.28711359509088</v>
+        <v>28.02035482708277</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22.60453722602316</v>
+        <v>26.2437160063069</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>24.85231018371906</v>
+        <v>27.31782191634802</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.33935632871305</v>
+        <v>26.93887700077238</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27.07059987099989</v>
+        <v>23.23250991983637</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28.11016181527857</v>
+        <v>25.46969572894216</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31.47959024504506</v>
+        <v>28.10478184531087</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>23.38570942280567</v>
+        <v>25.97067828223002</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>26.1371467581629</v>
+        <v>25.67122396987591</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>28.03970894712026</v>
+        <v>28.66885722785473</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28.212374127325</v>
+        <v>32.27189420002878</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28.84210424282772</v>
+        <v>30.28767579581057</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>26.69020429004637</v>
+        <v>29.29292802813542</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>19.75219788355927</v>
+        <v>22.81422961160288</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>26.42486760863856</v>
+        <v>25.86373862885517</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>28.02967681343226</v>
+        <v>28.82646197585879</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>28.39713287858624</v>
+        <v>32.11767526528895</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.2031900523051</v>
+        <v>30.12867002974292</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>27.68916018813398</v>
+        <v>29.64239832656851</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>19.43931321348244</v>
+        <v>22.32329964241104</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>26.0905846833175</v>
+        <v>25.69122263427757</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>28.62041872317977</v>
+        <v>28.66571009709022</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>27.8724109715357</v>
+        <v>32.027332965879</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>29.60361593354917</v>
+        <v>30.17251642061083</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>27.3618845742841</v>
+        <v>29.67347182633418</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>19.54818143265341</v>
+        <v>22.34452721397565</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>26.02593266782886</v>
+        <v>25.8500999319309</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>28.19068770570833</v>
+        <v>28.28031124345716</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>28.44119056595101</v>
+        <v>32.46066280958888</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28.47279589487055</v>
+        <v>29.59173610596198</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>27.05228344350408</v>
+        <v>29.75446482182123</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>19.14166797427867</v>
+        <v>22.63040605345752</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>25.32133056938052</v>
+        <v>26.82663542103833</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29.49476501632238</v>
+        <v>32.48509370574104</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>29.36333097722495</v>
+        <v>26.53185073594661</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30.05243924239526</v>
+        <v>26.73211569237938</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>29.93940170619767</v>
+        <v>30.00471036942374</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>23.98833981925803</v>
+        <v>34.61365181451028</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>25.30117297900549</v>
+        <v>27.26999239650895</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30.19367348056218</v>
+        <v>32.84953410254846</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>29.66163319429181</v>
+        <v>25.88396420269155</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>29.68374460842151</v>
+        <v>26.44275035667281</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29.46502631388352</v>
+        <v>30.51743414876423</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24.25869794806401</v>
+        <v>33.98450856041985</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>25.68709171745893</v>
+        <v>26.50317648477707</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30.35461276894996</v>
+        <v>32.91911265385792</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>29.75937443603431</v>
+        <v>26.40585097750185</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>29.56286719937211</v>
+        <v>26.0529448033841</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>29.77249555715134</v>
+        <v>30.73190093763537</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>24.04908380857763</v>
+        <v>33.79973332458925</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>25.26614135341444</v>
+        <v>27.04840625087371</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29.96696325590481</v>
+        <v>32.75411849151376</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>29.09383101197953</v>
+        <v>26.14927241447303</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>30.04868318147007</v>
+        <v>26.18973807227766</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.04444271535057</v>
+        <v>30.83838881575773</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>23.85399680796633</v>
+        <v>34.44756823877528</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios144.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.65046748039528</v>
+        <v>35.00802662281025</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.24656289412541</v>
+        <v>23.87687209317568</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.59733377173156</v>
+        <v>25.94403887790209</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.29044511696442</v>
+        <v>27.58219010615251</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.86276231189549</v>
+        <v>34.42160755688112</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.9703314553703</v>
+        <v>31.35587871684238</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.54644560041393</v>
+        <v>35.57226052779636</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.23858595052071</v>
+        <v>24.03026640211656</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.73484279650808</v>
+        <v>26.19587140074465</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.61615785453955</v>
+        <v>27.55899205137318</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.27971679549439</v>
+        <v>34.37887274335901</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.31683116174625</v>
+        <v>31.61539961983002</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.37399833765323</v>
+        <v>35.34301159359618</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.41237969365224</v>
+        <v>23.84174303562957</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.65163154539501</v>
+        <v>25.96558905778368</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.30419008282835</v>
+        <v>27.00157379353944</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.33896515943905</v>
+        <v>34.65972413883942</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.04717455991932</v>
+        <v>31.6030121058513</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.9702183921431</v>
+        <v>35.00222653209866</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>26.48201475215965</v>
+        <v>24.03850961310767</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.07850287784662</v>
+        <v>25.94094149424773</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.02541697054046</v>
+        <v>27.49015767725365</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.77470744571601</v>
+        <v>34.85059085750135</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.92679089301319</v>
+        <v>31.77142612408049</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.03738452070349</v>
+        <v>29.78489360192292</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27.12468397564772</v>
+        <v>28.70002880956921</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23.3936326227774</v>
+        <v>22.62831387713481</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.11506478789694</v>
+        <v>22.3000042069768</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27.90056655146273</v>
+        <v>28.70411323450095</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.16547251859039</v>
+        <v>26.45573046728104</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.056296015821</v>
+        <v>29.35759734658227</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27.09398799783844</v>
+        <v>29.07517606027571</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>23.2681794878276</v>
+        <v>22.27503835911642</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25.58196303637139</v>
+        <v>22.65603939545262</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.0384731664301</v>
+        <v>29.09110199533267</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26.05701896004416</v>
+        <v>26.20097020652441</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.04771321096216</v>
+        <v>29.88762809526206</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.92109046683074</v>
+        <v>29.60977874255009</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>23.16362784684978</v>
+        <v>22.80330462833202</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.73020673079117</v>
+        <v>22.41336998036659</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.02035482708277</v>
+        <v>28.64621360094677</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.2437160063069</v>
+        <v>26.89034806368617</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.31782191634802</v>
+        <v>29.33061455422785</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>26.93887700077238</v>
+        <v>29.41408359601412</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>23.23250991983637</v>
+        <v>22.58457583981468</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25.46969572894216</v>
+        <v>22.67306217087094</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.10478184531087</v>
+        <v>29.05945394519821</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25.97067828223002</v>
+        <v>26.79777841070672</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25.67122396987591</v>
+        <v>32.571262604371</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>28.66885722785473</v>
+        <v>31.9268315663335</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>32.27189420002878</v>
+        <v>24.52050545439058</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30.28767579581057</v>
+        <v>27.26270669042598</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>29.29292802813542</v>
+        <v>27.3600488165036</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>22.81422961160288</v>
+        <v>20.18615252873585</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25.86373862885517</v>
+        <v>32.15407341479393</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>28.82646197585879</v>
+        <v>31.67073098076687</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32.11767526528895</v>
+        <v>24.20213423082156</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.12867002974292</v>
+        <v>27.68131449351691</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>29.64239832656851</v>
+        <v>26.74326645283131</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.32329964241104</v>
+        <v>20.30898636436698</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>25.69122263427757</v>
+        <v>33.1941037137777</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>28.66571009709022</v>
+        <v>31.83105167042734</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>32.027332965879</v>
+        <v>24.94677987074981</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>30.17251642061083</v>
+        <v>27.39957560852063</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>29.67347182633418</v>
+        <v>26.62306462165199</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.34452721397565</v>
+        <v>20.85276619951922</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>25.8500999319309</v>
+        <v>32.48056005709363</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>28.28031124345716</v>
+        <v>31.61836737461469</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>32.46066280958888</v>
+        <v>24.72140197622167</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>29.59173610596198</v>
+        <v>27.11146155169386</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>29.75446482182123</v>
+        <v>27.01924807356566</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.63040605345752</v>
+        <v>20.65063132900828</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>26.82663542103833</v>
+        <v>24.14235362500137</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>32.48509370574104</v>
+        <v>33.09428773295588</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>26.53185073594661</v>
+        <v>24.08397050475167</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.73211569237938</v>
+        <v>27.12851045045102</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30.00471036942374</v>
+        <v>26.05934810368815</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>34.61365181451028</v>
+        <v>28.9887701701911</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>27.26999239650895</v>
+        <v>23.94715411366396</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>32.84953410254846</v>
+        <v>34.08097489968596</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>25.88396420269155</v>
+        <v>24.17379030489381</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>26.44275035667281</v>
+        <v>26.88248330997454</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30.51743414876423</v>
+        <v>26.03957551608741</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>33.98450856041985</v>
+        <v>29.18876835825949</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>26.50317648477707</v>
+        <v>23.88962719340272</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>32.91911265385792</v>
+        <v>33.47282230252298</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>26.40585097750185</v>
+        <v>23.8596748640931</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26.0529448033841</v>
+        <v>26.95449609286213</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>30.73190093763537</v>
+        <v>26.39292065584362</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>33.79973332458925</v>
+        <v>28.97173865062402</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>27.04840625087371</v>
+        <v>24.14706325483539</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>32.75411849151376</v>
+        <v>33.09640899429669</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26.14927241447303</v>
+        <v>23.65427040180646</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26.18973807227766</v>
+        <v>26.89103201788812</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.83838881575773</v>
+        <v>26.2853517350126</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>34.44756823877528</v>
+        <v>29.21657606323191</v>
       </c>
     </row>
   </sheetData>
